--- a/sentinal_ihsan/could-you-survive/series_log.xlsx
+++ b/sentinal_ihsan/could-you-survive/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2221,6 +2221,352 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-18 19:46</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/95d4a1061d2f322cb2df17c6f31fb463_1784403809.mp4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-18 19:48</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8760ccfe4555505a5d9bf44d148329c3_1784404096.mp4</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-18 19:53</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/bc6ea493766f0e1989065b3a275018f1_1784404239.mp4</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep06/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-18 19:59</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/fa356d5f354cb97049234aac628eef52_1784404570.mp4</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep06/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-18 20:01</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ca71495347b221cc75aed2f74c292910_1784404880.mp4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep06/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-18 20:05</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6ae2d66bd7dd9f6b32887916742e6f8c_1784405077.mp4</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep06/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinal_ihsan/could-you-survive/series_log.xlsx
+++ b/sentinal_ihsan/could-you-survive/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2567,6 +2567,352 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-19 19:44</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b79f7e6bb1bfb1e4ebf12431b958503d_1784490247.mp4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-19 19:50</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0716c5cd40bbc0bb5947f6335a9781d6_1784490434.mp4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep07/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-19 19:52</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ccca05fbf527bcba7c06ae9b62f3dc50_1784490738.mp4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep07/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-19 20:03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1.575</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/363d2bf4c04610a442b604d47d018459_1784490899.mp4</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep07/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-19 20:06</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f9b65d7714c5642140f3cc55261e3fbc_1784491538.mp4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep07/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-19 20:09</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ed7ff5983a07885dd7d9520e6f6690e3_1784491697.mp4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep07/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
